--- a/backend/scripts/fixtures/demo_register.xlsx
+++ b/backend/scripts/fixtures/demo_register.xlsx
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Taxable Amount BDT</t>
+          <t>Taxable Amount (BDT)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>VAT Amount BDT</t>
+          <t>VAT Amount (BDT)</t>
         </is>
       </c>
     </row>

--- a/backend/scripts/fixtures/demo_register.xlsx
+++ b/backend/scripts/fixtures/demo_register.xlsx
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>567890123</t>
+          <t>888777666</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pran-RFL Group</t>
+          <t>Off-Pool Supplier A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>123456789</t>
+          <t>888777555</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bashundhara Industries Ltd</t>
+          <t>Off-Pool Supplier B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
